--- a/workbooks/methodology/scoring_logic/implied_weights_summary.xlsx
+++ b/workbooks/methodology/scoring_logic/implied_weights_summary.xlsx
@@ -465,7 +465,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>789</v>
+        <v>834</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -473,19 +473,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.261238</v>
+        <v>0.199053</v>
       </c>
       <c r="E2" t="n">
         <v>0.3</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.038762</v>
+        <v>-0.100947</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9442</v>
+        <v>0.9448</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5147</v>
+        <v>0.6083</v>
       </c>
     </row>
     <row r="3">
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>789</v>
+        <v>834</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -503,19 +503,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.365946</v>
+        <v>0.428915</v>
       </c>
       <c r="E3" t="n">
         <v>0.35</v>
       </c>
       <c r="F3" t="n">
-        <v>0.015946</v>
+        <v>0.078915</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9442</v>
+        <v>0.9448</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5147</v>
+        <v>0.6083</v>
       </c>
     </row>
     <row r="4">
@@ -525,7 +525,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>789</v>
+        <v>834</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -533,19 +533,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.275561</v>
+        <v>0.292104</v>
       </c>
       <c r="E4" t="n">
         <v>0.2</v>
       </c>
       <c r="F4" t="n">
-        <v>0.075561</v>
+        <v>0.09210400000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9442</v>
+        <v>0.9448</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5147</v>
+        <v>0.6083</v>
       </c>
     </row>
     <row r="5">
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>789</v>
+        <v>834</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -563,19 +563,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.097256</v>
+        <v>0.079928</v>
       </c>
       <c r="E5" t="n">
         <v>0.15</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.052744</v>
+        <v>-0.070072</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9442</v>
+        <v>0.9448</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5147</v>
+        <v>0.6083</v>
       </c>
     </row>
     <row r="6">
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>384</v>
+        <v>309</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.589859</v>
+        <v>0.631899</v>
       </c>
       <c r="E6" t="n">
         <v>0.3</v>
       </c>
       <c r="F6" t="n">
-        <v>0.289859</v>
+        <v>0.331899</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8672</v>
+        <v>0.9191</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5216</v>
+        <v>0.7127</v>
       </c>
     </row>
     <row r="7">
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>384</v>
+        <v>309</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -632,10 +632,10 @@
         <v>-0.35</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8672</v>
+        <v>0.9191</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5216</v>
+        <v>0.7127</v>
       </c>
     </row>
     <row r="8">
@@ -645,7 +645,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>384</v>
+        <v>309</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.325874</v>
+        <v>0.368101</v>
       </c>
       <c r="E8" t="n">
         <v>0.2</v>
       </c>
       <c r="F8" t="n">
-        <v>0.125874</v>
+        <v>0.168101</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8672</v>
+        <v>0.9191</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5216</v>
+        <v>0.7127</v>
       </c>
     </row>
     <row r="9">
@@ -675,7 +675,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>384</v>
+        <v>309</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -683,19 +683,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.08426599999999999</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
         <v>0.15</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.065734</v>
+        <v>-0.15</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8672</v>
+        <v>0.9191</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5216</v>
+        <v>0.7127</v>
       </c>
     </row>
     <row r="10">
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>240</v>
+        <v>294</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -713,19 +713,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.225409</v>
+        <v>0.169916</v>
       </c>
       <c r="E10" t="n">
         <v>0.3</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.074591</v>
+        <v>-0.130084</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9833</v>
+        <v>0.966</v>
       </c>
       <c r="H10" t="n">
-        <v>0.5978</v>
+        <v>0.5859</v>
       </c>
     </row>
     <row r="11">
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>240</v>
+        <v>294</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -743,19 +743,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.456338</v>
+        <v>0.5237849999999999</v>
       </c>
       <c r="E11" t="n">
         <v>0.35</v>
       </c>
       <c r="F11" t="n">
-        <v>0.106338</v>
+        <v>0.173785</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9833</v>
+        <v>0.966</v>
       </c>
       <c r="H11" t="n">
-        <v>0.5978</v>
+        <v>0.5859</v>
       </c>
     </row>
     <row r="12">
@@ -765,7 +765,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>240</v>
+        <v>294</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -773,19 +773,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.080855</v>
+        <v>0.092489</v>
       </c>
       <c r="E12" t="n">
         <v>0.2</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.119145</v>
+        <v>-0.107511</v>
       </c>
       <c r="G12" t="n">
-        <v>0.9833</v>
+        <v>0.966</v>
       </c>
       <c r="H12" t="n">
-        <v>0.5978</v>
+        <v>0.5859</v>
       </c>
     </row>
     <row r="13">
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>240</v>
+        <v>294</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -803,19 +803,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.237398</v>
+        <v>0.21381</v>
       </c>
       <c r="E13" t="n">
         <v>0.15</v>
       </c>
       <c r="F13" t="n">
-        <v>0.087398</v>
+        <v>0.06381000000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>0.9833</v>
+        <v>0.966</v>
       </c>
       <c r="H13" t="n">
-        <v>0.5978</v>
+        <v>0.5859</v>
       </c>
     </row>
     <row r="14">
@@ -825,7 +825,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>165</v>
+        <v>231</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -833,19 +833,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.101385</v>
+        <v>0.212651</v>
       </c>
       <c r="E14" t="n">
         <v>0.3</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.198615</v>
+        <v>-0.087349</v>
       </c>
       <c r="G14" t="n">
-        <v>0.9939</v>
+        <v>0.9654</v>
       </c>
       <c r="H14" t="n">
-        <v>0.134</v>
+        <v>0.5024999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -855,7 +855,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>165</v>
+        <v>231</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -863,19 +863,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.592574</v>
+        <v>0.410353</v>
       </c>
       <c r="E15" t="n">
         <v>0.35</v>
       </c>
       <c r="F15" t="n">
-        <v>0.242574</v>
+        <v>0.060353</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9939</v>
+        <v>0.9654</v>
       </c>
       <c r="H15" t="n">
-        <v>0.134</v>
+        <v>0.5024999999999999</v>
       </c>
     </row>
     <row r="16">
@@ -885,7 +885,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>165</v>
+        <v>231</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -893,19 +893,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.145128</v>
+        <v>0.147684</v>
       </c>
       <c r="E16" t="n">
         <v>0.2</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.054872</v>
+        <v>-0.052316</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9939</v>
+        <v>0.9654</v>
       </c>
       <c r="H16" t="n">
-        <v>0.134</v>
+        <v>0.5024999999999999</v>
       </c>
     </row>
     <row r="17">
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>165</v>
+        <v>231</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -923,19 +923,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.160913</v>
+        <v>0.229312</v>
       </c>
       <c r="E17" t="n">
         <v>0.15</v>
       </c>
       <c r="F17" t="n">
-        <v>0.010913</v>
+        <v>0.07931199999999999</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9939</v>
+        <v>0.9654</v>
       </c>
       <c r="H17" t="n">
-        <v>0.134</v>
+        <v>0.5024999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/workbooks/methodology/scoring_logic/implied_weights_summary.xlsx
+++ b/workbooks/methodology/scoring_logic/implied_weights_summary.xlsx
@@ -465,7 +465,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>834</v>
+        <v>828</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -473,19 +473,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.199053</v>
+        <v>0.198658</v>
       </c>
       <c r="E2" t="n">
         <v>0.3</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.100947</v>
+        <v>-0.101342</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9448</v>
+        <v>0.9444</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6083</v>
+        <v>0.6072</v>
       </c>
     </row>
     <row r="3">
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>834</v>
+        <v>828</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -503,19 +503,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.428915</v>
+        <v>0.429764</v>
       </c>
       <c r="E3" t="n">
         <v>0.35</v>
       </c>
       <c r="F3" t="n">
-        <v>0.078915</v>
+        <v>0.079764</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9448</v>
+        <v>0.9444</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6083</v>
+        <v>0.6072</v>
       </c>
     </row>
     <row r="4">
@@ -525,7 +525,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>834</v>
+        <v>828</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -533,19 +533,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.292104</v>
+        <v>0.292436</v>
       </c>
       <c r="E4" t="n">
         <v>0.2</v>
       </c>
       <c r="F4" t="n">
-        <v>0.09210400000000001</v>
+        <v>0.092436</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9448</v>
+        <v>0.9444</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6083</v>
+        <v>0.6072</v>
       </c>
     </row>
     <row r="5">
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>834</v>
+        <v>828</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -563,19 +563,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.079928</v>
+        <v>0.079141</v>
       </c>
       <c r="E5" t="n">
         <v>0.15</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.070072</v>
+        <v>-0.07085900000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9448</v>
+        <v>0.9444</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6083</v>
+        <v>0.6072</v>
       </c>
     </row>
     <row r="6">
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -713,19 +713,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.169916</v>
+        <v>0.169869</v>
       </c>
       <c r="E10" t="n">
         <v>0.3</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.130084</v>
+        <v>-0.130131</v>
       </c>
       <c r="G10" t="n">
-        <v>0.966</v>
+        <v>0.9653</v>
       </c>
       <c r="H10" t="n">
-        <v>0.5859</v>
+        <v>0.5847</v>
       </c>
     </row>
     <row r="11">
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -743,19 +743,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.5237849999999999</v>
+        <v>0.5239239999999999</v>
       </c>
       <c r="E11" t="n">
         <v>0.35</v>
       </c>
       <c r="F11" t="n">
-        <v>0.173785</v>
+        <v>0.173924</v>
       </c>
       <c r="G11" t="n">
-        <v>0.966</v>
+        <v>0.9653</v>
       </c>
       <c r="H11" t="n">
-        <v>0.5859</v>
+        <v>0.5847</v>
       </c>
     </row>
     <row r="12">
@@ -765,7 +765,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -773,19 +773,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.092489</v>
+        <v>0.094564</v>
       </c>
       <c r="E12" t="n">
         <v>0.2</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.107511</v>
+        <v>-0.105436</v>
       </c>
       <c r="G12" t="n">
-        <v>0.966</v>
+        <v>0.9653</v>
       </c>
       <c r="H12" t="n">
-        <v>0.5859</v>
+        <v>0.5847</v>
       </c>
     </row>
     <row r="13">
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -803,19 +803,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.21381</v>
+        <v>0.211643</v>
       </c>
       <c r="E13" t="n">
         <v>0.15</v>
       </c>
       <c r="F13" t="n">
-        <v>0.06381000000000001</v>
+        <v>0.061643</v>
       </c>
       <c r="G13" t="n">
-        <v>0.966</v>
+        <v>0.9653</v>
       </c>
       <c r="H13" t="n">
-        <v>0.5859</v>
+        <v>0.5847</v>
       </c>
     </row>
     <row r="14">

--- a/workbooks/methodology/scoring_logic/implied_weights_summary.xlsx
+++ b/workbooks/methodology/scoring_logic/implied_weights_summary.xlsx
@@ -465,7 +465,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>828</v>
+        <v>855</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -473,19 +473,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.198658</v>
+        <v>0.212229</v>
       </c>
       <c r="E2" t="n">
         <v>0.3</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.101342</v>
+        <v>-0.087771</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9444</v>
+        <v>0.952</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6072</v>
+        <v>0.603</v>
       </c>
     </row>
     <row r="3">
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>828</v>
+        <v>855</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -503,19 +503,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.429764</v>
+        <v>0.418194</v>
       </c>
       <c r="E3" t="n">
         <v>0.35</v>
       </c>
       <c r="F3" t="n">
-        <v>0.079764</v>
+        <v>0.068194</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9444</v>
+        <v>0.952</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6072</v>
+        <v>0.603</v>
       </c>
     </row>
     <row r="4">
@@ -525,7 +525,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>828</v>
+        <v>855</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -533,19 +533,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.292436</v>
+        <v>0.292554</v>
       </c>
       <c r="E4" t="n">
         <v>0.2</v>
       </c>
       <c r="F4" t="n">
-        <v>0.092436</v>
+        <v>0.092554</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9444</v>
+        <v>0.952</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6072</v>
+        <v>0.603</v>
       </c>
     </row>
     <row r="5">
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>828</v>
+        <v>855</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -563,19 +563,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.079141</v>
+        <v>0.07702299999999999</v>
       </c>
       <c r="E5" t="n">
         <v>0.15</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.07085900000000001</v>
+        <v>-0.072977</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9444</v>
+        <v>0.952</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6072</v>
+        <v>0.603</v>
       </c>
     </row>
     <row r="6">
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.631899</v>
+        <v>0.621198</v>
       </c>
       <c r="E6" t="n">
         <v>0.3</v>
       </c>
       <c r="F6" t="n">
-        <v>0.331899</v>
+        <v>0.321198</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9191</v>
+        <v>0.9333</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7127</v>
+        <v>0.7159</v>
       </c>
     </row>
     <row r="7">
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -632,10 +632,10 @@
         <v>-0.35</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9191</v>
+        <v>0.9333</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7127</v>
+        <v>0.7159</v>
       </c>
     </row>
     <row r="8">
@@ -645,7 +645,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.368101</v>
+        <v>0.378802</v>
       </c>
       <c r="E8" t="n">
         <v>0.2</v>
       </c>
       <c r="F8" t="n">
-        <v>0.168101</v>
+        <v>0.178802</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9191</v>
+        <v>0.9333</v>
       </c>
       <c r="H8" t="n">
-        <v>0.7127</v>
+        <v>0.7159</v>
       </c>
     </row>
     <row r="9">
@@ -675,7 +675,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -692,10 +692,10 @@
         <v>-0.15</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9191</v>
+        <v>0.9333</v>
       </c>
       <c r="H9" t="n">
-        <v>0.7127</v>
+        <v>0.7159</v>
       </c>
     </row>
     <row r="10">
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>288</v>
+        <v>300</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -713,19 +713,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.169869</v>
+        <v>0.183821</v>
       </c>
       <c r="E10" t="n">
         <v>0.3</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.130131</v>
+        <v>-0.116179</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9653</v>
+        <v>0.9633</v>
       </c>
       <c r="H10" t="n">
-        <v>0.5847</v>
+        <v>0.5891999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>288</v>
+        <v>300</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -743,19 +743,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.5239239999999999</v>
+        <v>0.507355</v>
       </c>
       <c r="E11" t="n">
         <v>0.35</v>
       </c>
       <c r="F11" t="n">
-        <v>0.173924</v>
+        <v>0.157355</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9653</v>
+        <v>0.9633</v>
       </c>
       <c r="H11" t="n">
-        <v>0.5847</v>
+        <v>0.5891999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -765,7 +765,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>288</v>
+        <v>300</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -773,19 +773,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.094564</v>
+        <v>0.117213</v>
       </c>
       <c r="E12" t="n">
         <v>0.2</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.105436</v>
+        <v>-0.082787</v>
       </c>
       <c r="G12" t="n">
-        <v>0.9653</v>
+        <v>0.9633</v>
       </c>
       <c r="H12" t="n">
-        <v>0.5847</v>
+        <v>0.5891999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>288</v>
+        <v>300</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -803,19 +803,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.211643</v>
+        <v>0.191611</v>
       </c>
       <c r="E13" t="n">
         <v>0.15</v>
       </c>
       <c r="F13" t="n">
-        <v>0.061643</v>
+        <v>0.041611</v>
       </c>
       <c r="G13" t="n">
-        <v>0.9653</v>
+        <v>0.9633</v>
       </c>
       <c r="H13" t="n">
-        <v>0.5847</v>
+        <v>0.5891999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -825,7 +825,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -833,19 +833,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.212651</v>
+        <v>0.253025</v>
       </c>
       <c r="E14" t="n">
         <v>0.3</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.087349</v>
+        <v>-0.046975</v>
       </c>
       <c r="G14" t="n">
-        <v>0.9654</v>
+        <v>0.9208</v>
       </c>
       <c r="H14" t="n">
-        <v>0.5024999999999999</v>
+        <v>0.4904</v>
       </c>
     </row>
     <row r="15">
@@ -855,7 +855,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -863,19 +863,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.410353</v>
+        <v>0.4002</v>
       </c>
       <c r="E15" t="n">
         <v>0.35</v>
       </c>
       <c r="F15" t="n">
-        <v>0.060353</v>
+        <v>0.0502</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9654</v>
+        <v>0.9208</v>
       </c>
       <c r="H15" t="n">
-        <v>0.5024999999999999</v>
+        <v>0.4904</v>
       </c>
     </row>
     <row r="16">
@@ -885,7 +885,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -893,19 +893,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.147684</v>
+        <v>0.049761</v>
       </c>
       <c r="E16" t="n">
         <v>0.2</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.052316</v>
+        <v>-0.150239</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9654</v>
+        <v>0.9208</v>
       </c>
       <c r="H16" t="n">
-        <v>0.5024999999999999</v>
+        <v>0.4904</v>
       </c>
     </row>
     <row r="17">
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -923,19 +923,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.229312</v>
+        <v>0.297014</v>
       </c>
       <c r="E17" t="n">
         <v>0.15</v>
       </c>
       <c r="F17" t="n">
-        <v>0.07931199999999999</v>
+        <v>0.147014</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9654</v>
+        <v>0.9208</v>
       </c>
       <c r="H17" t="n">
-        <v>0.5024999999999999</v>
+        <v>0.4904</v>
       </c>
     </row>
   </sheetData>

--- a/workbooks/methodology/scoring_logic/implied_weights_summary.xlsx
+++ b/workbooks/methodology/scoring_logic/implied_weights_summary.xlsx
@@ -473,19 +473,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.212229</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
         <v>0.3</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.087771</v>
+        <v>-0.3</v>
       </c>
       <c r="G2" t="n">
-        <v>0.952</v>
+        <v>0.752</v>
       </c>
       <c r="H2" t="n">
-        <v>0.603</v>
+        <v>0.0259</v>
       </c>
     </row>
     <row r="3">
@@ -503,19 +503,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.418194</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
         <v>0.35</v>
       </c>
       <c r="F3" t="n">
-        <v>0.068194</v>
+        <v>-0.35</v>
       </c>
       <c r="G3" t="n">
-        <v>0.952</v>
+        <v>0.752</v>
       </c>
       <c r="H3" t="n">
-        <v>0.603</v>
+        <v>0.0259</v>
       </c>
     </row>
     <row r="4">
@@ -533,19 +533,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.292554</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
         <v>0.2</v>
       </c>
       <c r="F4" t="n">
-        <v>0.092554</v>
+        <v>0.8</v>
       </c>
       <c r="G4" t="n">
-        <v>0.952</v>
+        <v>0.752</v>
       </c>
       <c r="H4" t="n">
-        <v>0.603</v>
+        <v>0.0259</v>
       </c>
     </row>
     <row r="5">
@@ -563,19 +563,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.07702299999999999</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
         <v>0.15</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.072977</v>
+        <v>-0.15</v>
       </c>
       <c r="G5" t="n">
-        <v>0.952</v>
+        <v>0.752</v>
       </c>
       <c r="H5" t="n">
-        <v>0.603</v>
+        <v>0.0259</v>
       </c>
     </row>
     <row r="6">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.621198</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
         <v>0.3</v>
       </c>
       <c r="F6" t="n">
-        <v>0.321198</v>
+        <v>-0.3</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9333</v>
+        <v>0.854</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7159</v>
+        <v>0.285</v>
       </c>
     </row>
     <row r="7">
@@ -632,10 +632,10 @@
         <v>-0.35</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9333</v>
+        <v>0.854</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7159</v>
+        <v>0.285</v>
       </c>
     </row>
     <row r="8">
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.378802</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
         <v>0.2</v>
       </c>
       <c r="F8" t="n">
-        <v>0.178802</v>
+        <v>0.8</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9333</v>
+        <v>0.854</v>
       </c>
       <c r="H8" t="n">
-        <v>0.7159</v>
+        <v>0.285</v>
       </c>
     </row>
     <row r="9">
@@ -692,10 +692,10 @@
         <v>-0.15</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9333</v>
+        <v>0.854</v>
       </c>
       <c r="H9" t="n">
-        <v>0.7159</v>
+        <v>0.285</v>
       </c>
     </row>
     <row r="10">
@@ -713,19 +713,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.183821</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
         <v>0.3</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.116179</v>
+        <v>-0.3</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9633</v>
+        <v>0.92</v>
       </c>
       <c r="H10" t="n">
-        <v>0.5891999999999999</v>
+        <v>-0.2108</v>
       </c>
     </row>
     <row r="11">
@@ -743,19 +743,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.507355</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
         <v>0.35</v>
       </c>
       <c r="F11" t="n">
-        <v>0.157355</v>
+        <v>-0.35</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9633</v>
+        <v>0.92</v>
       </c>
       <c r="H11" t="n">
-        <v>0.5891999999999999</v>
+        <v>-0.2108</v>
       </c>
     </row>
     <row r="12">
@@ -773,19 +773,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.117213</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
         <v>0.2</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.082787</v>
+        <v>-0.2</v>
       </c>
       <c r="G12" t="n">
-        <v>0.9633</v>
+        <v>0.92</v>
       </c>
       <c r="H12" t="n">
-        <v>0.5891999999999999</v>
+        <v>-0.2108</v>
       </c>
     </row>
     <row r="13">
@@ -803,19 +803,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.191611</v>
+        <v>1</v>
       </c>
       <c r="E13" t="n">
         <v>0.15</v>
       </c>
       <c r="F13" t="n">
-        <v>0.041611</v>
+        <v>0.85</v>
       </c>
       <c r="G13" t="n">
-        <v>0.9633</v>
+        <v>0.92</v>
       </c>
       <c r="H13" t="n">
-        <v>0.5891999999999999</v>
+        <v>-0.2108</v>
       </c>
     </row>
     <row r="14">
@@ -833,19 +833,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.253025</v>
+        <v>0.211194</v>
       </c>
       <c r="E14" t="n">
         <v>0.3</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.046975</v>
+        <v>-0.088806</v>
       </c>
       <c r="G14" t="n">
-        <v>0.9208</v>
+        <v>0.8375</v>
       </c>
       <c r="H14" t="n">
-        <v>0.4904</v>
+        <v>-0.2868</v>
       </c>
     </row>
     <row r="15">
@@ -863,19 +863,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.4002</v>
+        <v>0.788806</v>
       </c>
       <c r="E15" t="n">
         <v>0.35</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0502</v>
+        <v>0.438806</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9208</v>
+        <v>0.8375</v>
       </c>
       <c r="H15" t="n">
-        <v>0.4904</v>
+        <v>-0.2868</v>
       </c>
     </row>
     <row r="16">
@@ -893,19 +893,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.049761</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
         <v>0.2</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.150239</v>
+        <v>-0.2</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9208</v>
+        <v>0.8375</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4904</v>
+        <v>-0.2868</v>
       </c>
     </row>
     <row r="17">
@@ -923,19 +923,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.297014</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
         <v>0.15</v>
       </c>
       <c r="F17" t="n">
-        <v>0.147014</v>
+        <v>-0.15</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9208</v>
+        <v>0.8375</v>
       </c>
       <c r="H17" t="n">
-        <v>0.4904</v>
+        <v>-0.2868</v>
       </c>
     </row>
   </sheetData>

--- a/workbooks/methodology/scoring_logic/implied_weights_summary.xlsx
+++ b/workbooks/methodology/scoring_logic/implied_weights_summary.xlsx
@@ -722,7 +722,7 @@
         <v>-0.3</v>
       </c>
       <c r="G10" t="n">
-        <v>0.92</v>
+        <v>0.9167</v>
       </c>
       <c r="H10" t="n">
         <v>-0.2108</v>
@@ -752,7 +752,7 @@
         <v>-0.35</v>
       </c>
       <c r="G11" t="n">
-        <v>0.92</v>
+        <v>0.9167</v>
       </c>
       <c r="H11" t="n">
         <v>-0.2108</v>
@@ -782,7 +782,7 @@
         <v>-0.2</v>
       </c>
       <c r="G12" t="n">
-        <v>0.92</v>
+        <v>0.9167</v>
       </c>
       <c r="H12" t="n">
         <v>-0.2108</v>
@@ -812,7 +812,7 @@
         <v>0.85</v>
       </c>
       <c r="G13" t="n">
-        <v>0.92</v>
+        <v>0.9167</v>
       </c>
       <c r="H13" t="n">
         <v>-0.2108</v>

--- a/workbooks/methodology/scoring_logic/implied_weights_summary.xlsx
+++ b/workbooks/methodology/scoring_logic/implied_weights_summary.xlsx
@@ -482,10 +482,10 @@
         <v>-0.3</v>
       </c>
       <c r="G2" t="n">
-        <v>0.752</v>
+        <v>0.7415</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0259</v>
+        <v>0.0196</v>
       </c>
     </row>
     <row r="3">
@@ -512,10 +512,10 @@
         <v>-0.35</v>
       </c>
       <c r="G3" t="n">
-        <v>0.752</v>
+        <v>0.7415</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0259</v>
+        <v>0.0196</v>
       </c>
     </row>
     <row r="4">
@@ -542,10 +542,10 @@
         <v>0.8</v>
       </c>
       <c r="G4" t="n">
-        <v>0.752</v>
+        <v>0.7415</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0259</v>
+        <v>0.0196</v>
       </c>
     </row>
     <row r="5">
@@ -572,10 +572,10 @@
         <v>-0.15</v>
       </c>
       <c r="G5" t="n">
-        <v>0.752</v>
+        <v>0.7415</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0259</v>
+        <v>0.0196</v>
       </c>
     </row>
     <row r="6">
@@ -722,7 +722,7 @@
         <v>-0.3</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9167</v>
+        <v>0.92</v>
       </c>
       <c r="H10" t="n">
         <v>-0.2108</v>
@@ -752,7 +752,7 @@
         <v>-0.35</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9167</v>
+        <v>0.92</v>
       </c>
       <c r="H11" t="n">
         <v>-0.2108</v>
@@ -782,7 +782,7 @@
         <v>-0.2</v>
       </c>
       <c r="G12" t="n">
-        <v>0.9167</v>
+        <v>0.92</v>
       </c>
       <c r="H12" t="n">
         <v>-0.2108</v>
@@ -812,7 +812,7 @@
         <v>0.85</v>
       </c>
       <c r="G13" t="n">
-        <v>0.9167</v>
+        <v>0.92</v>
       </c>
       <c r="H13" t="n">
         <v>-0.2108</v>

--- a/workbooks/methodology/scoring_logic/implied_weights_summary.xlsx
+++ b/workbooks/methodology/scoring_logic/implied_weights_summary.xlsx
@@ -482,10 +482,10 @@
         <v>-0.3</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7415</v>
+        <v>0.7474</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0196</v>
+        <v>0.0264</v>
       </c>
     </row>
     <row r="3">
@@ -512,10 +512,10 @@
         <v>-0.35</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7415</v>
+        <v>0.7474</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0196</v>
+        <v>0.0264</v>
       </c>
     </row>
     <row r="4">
@@ -542,10 +542,10 @@
         <v>0.8</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7415</v>
+        <v>0.7474</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0196</v>
+        <v>0.0264</v>
       </c>
     </row>
     <row r="5">
@@ -572,10 +572,10 @@
         <v>-0.15</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7415</v>
+        <v>0.7474</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0196</v>
+        <v>0.0264</v>
       </c>
     </row>
     <row r="6">
@@ -833,19 +833,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.211194</v>
+        <v>0.25597</v>
       </c>
       <c r="E14" t="n">
         <v>0.3</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.088806</v>
+        <v>-0.04403</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8375</v>
+        <v>0.8292</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.2868</v>
+        <v>-0.2459</v>
       </c>
     </row>
     <row r="15">
@@ -863,19 +863,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.788806</v>
+        <v>0.74403</v>
       </c>
       <c r="E15" t="n">
         <v>0.35</v>
       </c>
       <c r="F15" t="n">
-        <v>0.438806</v>
+        <v>0.39403</v>
       </c>
       <c r="G15" t="n">
-        <v>0.8375</v>
+        <v>0.8292</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.2868</v>
+        <v>-0.2459</v>
       </c>
     </row>
     <row r="16">
@@ -902,10 +902,10 @@
         <v>-0.2</v>
       </c>
       <c r="G16" t="n">
-        <v>0.8375</v>
+        <v>0.8292</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.2868</v>
+        <v>-0.2459</v>
       </c>
     </row>
     <row r="17">
@@ -932,10 +932,10 @@
         <v>-0.15</v>
       </c>
       <c r="G17" t="n">
-        <v>0.8375</v>
+        <v>0.8292</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2868</v>
+        <v>-0.2459</v>
       </c>
     </row>
   </sheetData>
